--- a/workspace/tracker/george_emil_job_tracker.xlsx
+++ b/workspace/tracker/george_emil_job_tracker.xlsx
@@ -23,7 +23,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -35,8 +35,12 @@
       <b val="1"/>
       <color rgb="00FFFFFF"/>
     </font>
+    <font>
+      <color rgb="000000FF"/>
+      <u val="single"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -46,6 +50,16 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="001F3864"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00EAF0FB"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFF00"/>
       </patternFill>
     </fill>
   </fills>
@@ -61,10 +75,19 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -431,7 +454,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q1"/>
+  <dimension ref="A1:Q2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -540,8 +563,90 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>Demo Tech Cairo</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>AI Engineer Intern</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>Cairo, Egypt</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>linkedin</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="n">
+        <v>92</v>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>top</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>ai_engineer</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>George's final-year status, Python and PyTorch expertise, and experience with FastAPI and Docker align perfectly with the intern role. The focus on LLM/RAG workflows matches his project background, making this a strong realistic fit.</t>
+        </is>
+      </c>
+      <c r="J2" s="4" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/demo-ai-intern</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+      <c r="N2" s="2" t="n"/>
+      <c r="O2" s="2" t="inlineStr">
+        <is>
+          <t>slug:demo-tech-cairo-ai-engineer-intern-linkedin</t>
+        </is>
+      </c>
+      <c r="P2" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-25T16:41:59.894068+00:00</t>
+        </is>
+      </c>
+      <c r="Q2" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-25T16:49:10+00:00</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:Q1"/>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J2" r:id="rId1"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -673,7 +778,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C3"/>
+  <dimension ref="A1:C6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -732,6 +837,57 @@
         </is>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-05-25T16:43:12+00:00</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>new_role</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Demo Tech Cairo — AI Engineer Intern [linkedin] score=92</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-05-25T16:45:43+00:00</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>cv_ready</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>slug=demo-tech-cairo-ai-engineer-intern-linkedin</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-05-25T16:49:10+00:00</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>letter_ready</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>slug=demo-tech-cairo-ai-engineer-intern-linkedin</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:C1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
